--- a/exports/trend_1d/PGEL_full_report.xlsx
+++ b/exports/trend_1d/PGEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>28.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42146</v>
+        <v>42149</v>
       </c>
       <c r="H2" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="I2" t="n">
         <v>12.27447342720459</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K2" t="n">
-        <v>65.33</v>
+        <v>56</v>
       </c>
       <c r="L2" t="n">
         <v>18.67</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>28.57</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42181</v>
+        <v>42184</v>
       </c>
       <c r="H3" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="I3" t="n">
         <v>10.28318689425102</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K3" t="n">
-        <v>15.38</v>
+        <v>11.11</v>
       </c>
       <c r="L3" t="n">
         <v>5.13</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>29.47</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42311</v>
+        <v>42312</v>
       </c>
       <c r="H4" t="n">
-        <v>16.65</v>
+        <v>13.3</v>
       </c>
       <c r="I4" t="n">
         <v>16.28398880194389</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K4" t="n">
-        <v>60.1</v>
+        <v>27.88</v>
       </c>
       <c r="L4" t="n">
         <v>16.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N4" t="n">
-        <v>16.94</v>
+        <v>20.12</v>
       </c>
       <c r="O4" t="n">
         <v>5.05</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>44.72</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42360</v>
+        <v>42361</v>
       </c>
       <c r="H5" t="n">
-        <v>12.6</v>
+        <v>14.95</v>
       </c>
       <c r="I5" t="n">
         <v>14.81814050513998</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" t="n">
-        <v>5.26</v>
+        <v>-12.41</v>
       </c>
       <c r="L5" t="n">
         <v>21.43</v>
@@ -726,7 +785,7 @@
         <v>5.98</v>
       </c>
       <c r="N5" t="n">
-        <v>8.630000000000001</v>
+        <v>18.65</v>
       </c>
       <c r="O5" t="n">
         <v>-20.12</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>26.46</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H6" t="n">
-        <v>13.5</v>
+        <v>12.55</v>
       </c>
       <c r="I6" t="n">
         <v>13.34841371311989</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.699999999999999</v>
+        <v>-16.05</v>
       </c>
       <c r="L6" t="n">
         <v>17.06</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>35.34</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42429</v>
+        <v>42430</v>
       </c>
       <c r="H7" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="I7" t="n">
         <v>11.63011015378395</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7" t="n">
-        <v>11.55</v>
+        <v>6.77</v>
       </c>
       <c r="L7" t="n">
         <v>10.36</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>29.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42531</v>
+        <v>42534</v>
       </c>
       <c r="H8" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="I8" t="n">
         <v>10.98435269500409</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.27</v>
+        <v>-6.84</v>
       </c>
       <c r="L8" t="n">
         <v>14.53</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>13.03</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42538</v>
+        <v>42541</v>
       </c>
       <c r="H9" t="n">
-        <v>10.9</v>
+        <v>12.35</v>
       </c>
       <c r="I9" t="n">
         <v>12.32077738169838</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-13.3</v>
       </c>
       <c r="L9" t="n">
-        <v>5.5</v>
+        <v>19.27</v>
       </c>
       <c r="M9" t="n">
         <v>5.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.29</v>
+        <v>13.3</v>
       </c>
       <c r="O9" t="n">
         <v>-2.68</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>19.12</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42682</v>
+        <v>42683</v>
       </c>
       <c r="H10" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
         <v>15.64398569698866</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K10" t="n">
-        <v>28.74</v>
+        <v>21.46</v>
       </c>
       <c r="L10" t="n">
         <v>10.12</v>
       </c>
       <c r="M10" t="n">
-        <v>4.84</v>
+        <v>5.66</v>
       </c>
       <c r="N10" t="n">
         <v>8.18</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>16.9</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H11" t="n">
-        <v>13.4</v>
+        <v>14.85</v>
       </c>
       <c r="I11" t="n">
         <v>14.7834615533677</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" t="n">
-        <v>10.67</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>6.67</v>
@@ -1068,7 +1199,7 @@
         <v>4.17</v>
       </c>
       <c r="N11" t="n">
-        <v>8.42</v>
+        <v>10.82</v>
       </c>
       <c r="O11" t="n">
         <v>-5.66</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>17.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43084</v>
+        <v>43087</v>
       </c>
       <c r="H12" t="n">
-        <v>39</v>
+        <v>38.05</v>
       </c>
       <c r="I12" t="n">
         <v>38.14415420614023</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K12" t="n">
-        <v>162.63</v>
+        <v>156.23</v>
       </c>
       <c r="L12" t="n">
         <v>9.43</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>236</v>
+        <v>237</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>13.89</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43103</v>
+        <v>43104</v>
       </c>
       <c r="H13" t="n">
-        <v>41.5</v>
+        <v>44.2</v>
       </c>
       <c r="I13" t="n">
         <v>43.33477577840071</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.07</v>
+        <v>-16.16</v>
       </c>
       <c r="L13" t="n">
-        <v>13.27</v>
+        <v>18.53</v>
       </c>
       <c r="M13" t="n">
         <v>1.18</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>14.98</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H14" t="n">
-        <v>40.3</v>
+        <v>35.3</v>
       </c>
       <c r="I14" t="n">
         <v>38.48958704773774</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.82</v>
+        <v>-20.14</v>
       </c>
       <c r="L14" t="n">
-        <v>11.54</v>
+        <v>22.96</v>
       </c>
       <c r="M14" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="N14" t="n">
-        <v>4.63</v>
+        <v>12.41</v>
       </c>
       <c r="O14" t="n">
         <v>6.51</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>24.6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43186</v>
+        <v>43187</v>
       </c>
       <c r="H15" t="n">
-        <v>26.8</v>
+        <v>31.6</v>
       </c>
       <c r="I15" t="n">
         <v>28.4737360700212</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K15" t="n">
-        <v>24.08</v>
+        <v>10.48</v>
       </c>
       <c r="L15" t="n">
         <v>12.61</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>32.67</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43222</v>
+        <v>43223</v>
       </c>
       <c r="H16" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="I16" t="n">
         <v>26.90270859342281</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K16" t="n">
-        <v>-13.92</v>
+        <v>-17.72</v>
       </c>
       <c r="L16" t="n">
         <v>19.15</v>
       </c>
       <c r="M16" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="N16" t="n">
         <v>4.72</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>16.14</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43248</v>
+        <v>43249</v>
       </c>
       <c r="H17" t="n">
-        <v>26.35</v>
+        <v>26.65</v>
       </c>
       <c r="I17" t="n">
         <v>26.45006966023408</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.35</v>
+        <v>-2.5</v>
       </c>
       <c r="L17" t="n">
-        <v>5.77</v>
+        <v>15.38</v>
       </c>
       <c r="M17" t="n">
-        <v>2.27</v>
+        <v>4.36</v>
       </c>
       <c r="N17" t="n">
         <v>19.77</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>18.18</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H18" t="n">
-        <v>22.2</v>
+        <v>21.15</v>
       </c>
       <c r="I18" t="n">
         <v>21.80427421768935</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.7</v>
+        <v>-20.64</v>
       </c>
       <c r="L18" t="n">
-        <v>17.07</v>
+        <v>20.83</v>
       </c>
       <c r="M18" t="n">
         <v>1.5</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>30.19</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43447</v>
+        <v>43448</v>
       </c>
       <c r="H19" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="I19" t="n">
         <v>11.31171295952707</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K19" t="n">
-        <v>55.08</v>
+        <v>46.1</v>
       </c>
       <c r="L19" t="n">
         <v>20.57</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>29.07</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="I20" t="n">
         <v>9.419722019060806</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K20" t="n">
-        <v>-14.04</v>
+        <v>-17.98</v>
       </c>
       <c r="L20" t="n">
-        <v>17.54</v>
+        <v>19.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>26.12</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43544</v>
+        <v>43546</v>
       </c>
       <c r="H21" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="I21" t="n">
         <v>8.510888454642417</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K21" t="n">
-        <v>17.65</v>
+        <v>8.02</v>
       </c>
       <c r="L21" t="n">
         <v>6.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>7.79</v>
       </c>
       <c r="N21" t="n">
         <v>20.57</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>18.85</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H22" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I22" t="n">
         <v>7.203401597930364</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>-15.12</v>
+        <v>-20.93</v>
       </c>
       <c r="L22" t="n">
-        <v>15.7</v>
+        <v>21.51</v>
       </c>
       <c r="M22" t="n">
         <v>3.49</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>20.47</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43612</v>
+        <v>43613</v>
       </c>
       <c r="H23" t="n">
-        <v>7.4</v>
+        <v>7.55</v>
       </c>
       <c r="I23" t="n">
         <v>7.430073545871752</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.82</v>
+        <v>-11.03</v>
       </c>
       <c r="L23" t="n">
-        <v>11.03</v>
+        <v>12.5</v>
       </c>
       <c r="M23" t="n">
         <v>14.06</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>18.46</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43623</v>
+        <v>43626</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="I24" t="n">
         <v>6.156424110649661</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K24" t="n">
-        <v>-17.88</v>
+        <v>-19.87</v>
       </c>
       <c r="L24" t="n">
-        <v>19.87</v>
+        <v>20.53</v>
       </c>
       <c r="M24" t="n">
         <v>5.07</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>25.2</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H25" t="n">
-        <v>5.15</v>
+        <v>5.4</v>
       </c>
       <c r="I25" t="n">
         <v>5.345623589083074</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K25" t="n">
-        <v>14.88</v>
+        <v>10.74</v>
       </c>
       <c r="L25" t="n">
         <v>8.26</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>21.41</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43752</v>
+        <v>43753</v>
       </c>
       <c r="H26" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>4.331763309414843</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>-19.44</v>
+        <v>-25.93</v>
       </c>
       <c r="L26" t="n">
-        <v>24.07</v>
+        <v>27.78</v>
       </c>
       <c r="M26" t="n">
         <v>1.12</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>45.02</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43809</v>
+        <v>43810</v>
       </c>
       <c r="H27" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="I27" t="n">
         <v>4.085016422038411</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K27" t="n">
-        <v>13.75</v>
+        <v>-3.75</v>
       </c>
       <c r="L27" t="n">
         <v>18.75</v>
@@ -1980,7 +2303,7 @@
         <v>2.78</v>
       </c>
       <c r="N27" t="n">
-        <v>11.43</v>
+        <v>20.29</v>
       </c>
       <c r="O27" t="n">
         <v>-8.050000000000001</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>28.23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43862</v>
+        <v>43864</v>
       </c>
       <c r="H28" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="I28" t="n">
         <v>6.533363181553162</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K28" t="n">
-        <v>61.45</v>
+        <v>54.22</v>
       </c>
       <c r="L28" t="n">
         <v>18.07</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>24.8</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43885</v>
+        <v>43886</v>
       </c>
       <c r="H29" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I29" t="n">
         <v>7.568595476311293</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.5</v>
+        <v>-21.87</v>
       </c>
       <c r="L29" t="n">
-        <v>14.84</v>
+        <v>23.44</v>
       </c>
       <c r="M29" t="n">
         <v>3.23</v>
       </c>
       <c r="N29" t="n">
-        <v>7.46</v>
+        <v>8.33</v>
       </c>
       <c r="O29" t="n">
         <v>-4.48</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>22.87</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43893</v>
+        <v>43894</v>
       </c>
       <c r="H30" t="n">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="I30" t="n">
         <v>6.257022226473649</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>-17.95</v>
+        <v>-22.44</v>
       </c>
       <c r="L30" t="n">
-        <v>17.95</v>
+        <v>22.44</v>
       </c>
       <c r="M30" t="n">
         <v>5.37</v>
       </c>
       <c r="N30" t="n">
-        <v>5.37</v>
+        <v>5.47</v>
       </c>
       <c r="O30" t="n">
         <v>8.33</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>23.61</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43929</v>
+        <v>43930</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I31" t="n">
         <v>3.294346483379488</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K31" t="n">
-        <v>47.11</v>
+        <v>44.63</v>
       </c>
       <c r="L31" t="n">
         <v>2.48</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>19.08</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43969</v>
+        <v>43970</v>
       </c>
       <c r="H32" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I32" t="n">
         <v>3.443708037129318</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K32" t="n">
-        <v>2.99</v>
+        <v>1.49</v>
       </c>
       <c r="L32" t="n">
         <v>5.97</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>21.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43986</v>
+        <v>43987</v>
       </c>
       <c r="H33" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I33" t="n">
         <v>4.00086214610615</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>-14.71</v>
+        <v>-26.47</v>
       </c>
       <c r="L33" t="n">
-        <v>17.65</v>
+        <v>26.47</v>
       </c>
       <c r="M33" t="n">
-        <v>4.05</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>4.41</v>
+        <v>10.26</v>
       </c>
       <c r="O33" t="n">
         <v>-1.45</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>18.25</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44027</v>
+        <v>44028</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I34" t="n">
         <v>3.990251403367201</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.98</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>10.47</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>21.71</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44046</v>
+        <v>44047</v>
       </c>
       <c r="H35" t="n">
-        <v>4.6</v>
+        <v>5.05</v>
       </c>
       <c r="I35" t="n">
         <v>4.632377769368166</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>-17.95</v>
+        <v>-29.49</v>
       </c>
       <c r="L35" t="n">
-        <v>17.95</v>
+        <v>29.49</v>
       </c>
       <c r="M35" t="n">
-        <v>3.61</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>10.84</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>20.88</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44116</v>
+        <v>44117</v>
       </c>
       <c r="H36" t="n">
-        <v>8.949999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I36" t="n">
         <v>8.500704332993823</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K36" t="n">
-        <v>77.23</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="L36" t="n">
         <v>14.85</v>
       </c>
       <c r="M36" t="n">
-        <v>4.79</v>
+        <v>5.03</v>
       </c>
       <c r="N36" t="n">
         <v>5.19</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>17.52</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44123</v>
+        <v>44124</v>
       </c>
       <c r="H37" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>9.560290387122752</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.41</v>
+        <v>-15.29</v>
       </c>
       <c r="L37" t="n">
-        <v>9.41</v>
+        <v>15.29</v>
       </c>
       <c r="M37" t="n">
         <v>5.33</v>
       </c>
       <c r="N37" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="O37" t="n">
         <v>-5.03</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>16.33</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44197</v>
+        <v>44200</v>
       </c>
       <c r="H38" t="n">
-        <v>13.8</v>
+        <v>13.45</v>
       </c>
       <c r="I38" t="n">
         <v>13.79847698296953</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K38" t="n">
-        <v>40.82</v>
+        <v>37.24</v>
       </c>
       <c r="L38" t="n">
         <v>2.04</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>20.91</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H39" t="n">
-        <v>15.75</v>
+        <v>16.5</v>
       </c>
       <c r="I39" t="n">
         <v>16.02632172962831</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>-17.1</v>
+        <v>-22.68</v>
       </c>
       <c r="L39" t="n">
-        <v>17.47</v>
+        <v>22.68</v>
       </c>
       <c r="M39" t="n">
         <v>5</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>15.68</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H40" t="n">
-        <v>42.9</v>
+        <v>40.75</v>
       </c>
       <c r="I40" t="n">
         <v>40.8096698031358</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K40" t="n">
-        <v>160</v>
+        <v>146.97</v>
       </c>
       <c r="L40" t="n">
         <v>3.03</v>
@@ -2721,7 +3200,7 @@
         <v>5.02</v>
       </c>
       <c r="N40" t="n">
-        <v>4.98</v>
+        <v>5.01</v>
       </c>
       <c r="O40" t="n">
         <v>4.76</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>16.53</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H41" t="n">
-        <v>35.6</v>
+        <v>37.4</v>
       </c>
       <c r="I41" t="n">
         <v>37.15713469785431</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K41" t="n">
-        <v>12.64</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L41" t="n">
         <v>4.79</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>15.81</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H42" t="n">
-        <v>41.25</v>
+        <v>39.4</v>
       </c>
       <c r="I42" t="n">
         <v>40.20048935906744</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K42" t="n">
-        <v>10.29</v>
+        <v>5.35</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>22.76</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44452</v>
+        <v>44453</v>
       </c>
       <c r="H43" t="n">
-        <v>36.85</v>
+        <v>39.75</v>
       </c>
       <c r="I43" t="n">
         <v>37.45596201354196</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" t="n">
-        <v>6.47</v>
+        <v>-0.89</v>
       </c>
       <c r="L43" t="n">
         <v>16.24</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>20.25</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H44" t="n">
-        <v>71.34999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I44" t="n">
         <v>70.27966769777497</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K44" t="n">
-        <v>79.5</v>
+        <v>72.08</v>
       </c>
       <c r="L44" t="n">
         <v>6.92</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>19.51</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44637</v>
+        <v>44641</v>
       </c>
       <c r="H45" t="n">
-        <v>67.25</v>
+        <v>71.7</v>
       </c>
       <c r="I45" t="n">
         <v>70.81496081244104</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>1.68</v>
+        <v>-4.82</v>
       </c>
       <c r="L45" t="n">
-        <v>3.8</v>
+        <v>6.58</v>
       </c>
       <c r="M45" t="n">
         <v>3.85</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>17.78</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H46" t="n">
-        <v>70.05</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="I46" t="n">
         <v>69.09661230279747</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.3</v>
+        <v>-8.16</v>
       </c>
       <c r="L46" t="n">
-        <v>6.56</v>
+        <v>11.3</v>
       </c>
       <c r="M46" t="n">
         <v>2.92</v>
       </c>
       <c r="N46" t="n">
-        <v>4.45</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>6.62</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>23.29</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H47" t="n">
-        <v>69.2</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="I47" t="n">
         <v>76.11215575018178</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.09</v>
+        <v>-18.22</v>
       </c>
       <c r="L47" t="n">
-        <v>13.9</v>
+        <v>23.92</v>
       </c>
       <c r="M47" t="n">
-        <v>3.56</v>
+        <v>9.25</v>
       </c>
       <c r="N47" t="n">
-        <v>8.82</v>
+        <v>12.5</v>
       </c>
       <c r="O47" t="n">
         <v>-6</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>19.81</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H48" t="n">
-        <v>108.65</v>
+        <v>105.25</v>
       </c>
       <c r="I48" t="n">
         <v>105.6971175325286</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K48" t="n">
-        <v>39.56</v>
+        <v>35.2</v>
       </c>
       <c r="L48" t="n">
         <v>2.89</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>9</v>
+      </c>
+      <c r="U48" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>19.94</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H49" t="n">
-        <v>122.8</v>
+        <v>127.5</v>
       </c>
       <c r="I49" t="n">
         <v>123.3253173182172</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>-16.67</v>
+        <v>-21.14</v>
       </c>
       <c r="L49" t="n">
-        <v>18.76</v>
+        <v>21.71</v>
       </c>
       <c r="M49" t="n">
         <v>7.27</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>15.58</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45126</v>
+        <v>45127</v>
       </c>
       <c r="H50" t="n">
-        <v>153.55</v>
+        <v>151.45</v>
       </c>
       <c r="I50" t="n">
         <v>153.0545501332676</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K50" t="n">
-        <v>20.43</v>
+        <v>18.78</v>
       </c>
       <c r="L50" t="n">
         <v>3.29</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>11.09</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45142</v>
+        <v>45145</v>
       </c>
       <c r="H51" t="n">
-        <v>156.3</v>
+        <v>161.15</v>
       </c>
       <c r="I51" t="n">
         <v>160.7279977199078</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.2</v>
+        <v>-6.4</v>
       </c>
       <c r="L51" t="n">
-        <v>4.32</v>
+        <v>13.3</v>
       </c>
       <c r="M51" t="n">
-        <v>1.2</v>
+        <v>2.69</v>
       </c>
       <c r="N51" t="n">
         <v>3.23</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.09</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H52" t="n">
-        <v>190.65</v>
+        <v>186</v>
       </c>
       <c r="I52" t="n">
         <v>186.7010586088226</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K52" t="n">
-        <v>18.31</v>
+        <v>15.42</v>
       </c>
       <c r="L52" t="n">
         <v>1.8</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>14.48</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H53" t="n">
-        <v>211.15</v>
+        <v>222.6</v>
       </c>
       <c r="I53" t="n">
         <v>212.9306425268537</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>-13.52</v>
+        <v>-19.68</v>
       </c>
       <c r="L53" t="n">
-        <v>14.97</v>
+        <v>20.97</v>
       </c>
       <c r="M53" t="n">
         <v>2.26</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>12.76</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45296</v>
+        <v>45299</v>
       </c>
       <c r="H54" t="n">
-        <v>222.8</v>
+        <v>215.55</v>
       </c>
       <c r="I54" t="n">
         <v>221.1109671009129</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K54" t="n">
-        <v>0.09</v>
+        <v>-3.17</v>
       </c>
       <c r="L54" t="n">
-        <v>4.31</v>
+        <v>5.03</v>
       </c>
       <c r="M54" t="n">
         <v>3</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>13.6</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H55" t="n">
-        <v>166.2</v>
+        <v>179.25</v>
       </c>
       <c r="I55" t="n">
         <v>175.3308413964241</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K55" t="n">
-        <v>22.89</v>
+        <v>16.84</v>
       </c>
       <c r="L55" t="n">
         <v>3.92</v>
       </c>
       <c r="M55" t="n">
-        <v>1.79</v>
+        <v>3.49</v>
       </c>
       <c r="N55" t="n">
         <v>10.39</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>17.3</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H56" t="n">
-        <v>609.85</v>
+        <v>538.65</v>
       </c>
       <c r="I56" t="n">
         <v>578.2863216995949</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K56" t="n">
-        <v>240.22</v>
+        <v>200.5</v>
       </c>
       <c r="L56" t="n">
         <v>4.6</v>
@@ -3633,7 +4304,7 @@
         <v>6.08</v>
       </c>
       <c r="N56" t="n">
-        <v>9.779999999999999</v>
+        <v>11.68</v>
       </c>
       <c r="O56" t="n">
         <v>7.85</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>7</v>
+      </c>
+      <c r="U56" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>26.8</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45603</v>
+        <v>45604</v>
       </c>
       <c r="H57" t="n">
-        <v>668.8</v>
+        <v>689.7</v>
       </c>
       <c r="I57" t="n">
         <v>670.5091809408309</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K57" t="n">
-        <v>-24.16</v>
+        <v>-28.04</v>
       </c>
       <c r="L57" t="n">
-        <v>26.8</v>
+        <v>29.03</v>
       </c>
       <c r="M57" t="n">
         <v>2.57</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>15.7</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H58" t="n">
-        <v>881.85</v>
+        <v>827.25</v>
       </c>
       <c r="I58" t="n">
         <v>865.1616500081326</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K58" t="n">
-        <v>27.86</v>
+        <v>19.94</v>
       </c>
       <c r="L58" t="n">
         <v>11.43</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>23.76</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H59" t="n">
-        <v>847.3</v>
+        <v>870.85</v>
       </c>
       <c r="I59" t="n">
         <v>865.559115395493</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.42</v>
+        <v>-5.27</v>
       </c>
       <c r="L59" t="n">
         <v>11.82</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>18.15</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H60" t="n">
-        <v>871.65</v>
+        <v>813</v>
       </c>
       <c r="I60" t="n">
         <v>821.3536989760519</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K60" t="n">
-        <v>0.09</v>
+        <v>-6.64</v>
       </c>
       <c r="L60" t="n">
-        <v>6.4</v>
+        <v>17.93</v>
       </c>
       <c r="M60" t="n">
-        <v>2.02</v>
+        <v>18.01</v>
       </c>
       <c r="N60" t="n">
         <v>6.96</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>20.81</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="H61" t="n">
-        <v>808.9</v>
+        <v>828</v>
       </c>
       <c r="I61" t="n">
         <v>809.2039082141214</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>-1.85</v>
       </c>
       <c r="L61" t="n">
         <v>23.99</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>11.43</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45875</v>
+        <v>45876</v>
       </c>
       <c r="H62" t="n">
-        <v>751.95</v>
+        <v>736.85</v>
       </c>
       <c r="I62" t="n">
         <v>747.6320766706224</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K62" t="n">
-        <v>-9.18</v>
+        <v>-11.01</v>
       </c>
       <c r="L62" t="n">
-        <v>9.41</v>
+        <v>13.95</v>
       </c>
       <c r="M62" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="N62" t="n">
         <v>4.92</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>11.36</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H63" t="n">
-        <v>553.15</v>
+        <v>585.95</v>
       </c>
       <c r="I63" t="n">
         <v>563.5067713927589</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K63" t="n">
-        <v>24.93</v>
+        <v>20.48</v>
       </c>
       <c r="L63" t="n">
         <v>2.06</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>14.13</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H64" t="n">
-        <v>550.1</v>
+        <v>528.3</v>
       </c>
       <c r="I64" t="n">
         <v>529.3628523674512</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.12</v>
+        <v>-9.84</v>
       </c>
       <c r="L64" t="n">
-        <v>6.63</v>
+        <v>11.9</v>
       </c>
       <c r="M64" t="n">
         <v>1.52</v>
       </c>
       <c r="N64" t="n">
-        <v>3.28</v>
+        <v>3.96</v>
       </c>
       <c r="O64" t="n">
         <v>5.93</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>10.32</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="H65" t="n">
-        <v>578.1</v>
+        <v>580.35</v>
       </c>
       <c r="I65" t="n">
         <v>578.7479742749892</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K65" t="n">
-        <v>-9.43</v>
+        <v>-9.85</v>
       </c>
       <c r="L65" t="n">
-        <v>10.16</v>
+        <v>11.02</v>
       </c>
       <c r="M65" t="n">
         <v>0.91</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>12.75</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H66" t="n">
-        <v>553.9</v>
+        <v>529.6</v>
       </c>
       <c r="I66" t="n">
         <v>533.973325422993</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.56</v>
+        <v>-8.74</v>
       </c>
       <c r="L66" t="n">
-        <v>6.21</v>
+        <v>10.14</v>
       </c>
       <c r="M66" t="n">
-        <v>0.66</v>
+        <v>1.43</v>
       </c>
       <c r="N66" t="n">
-        <v>4.34</v>
+        <v>4.39</v>
       </c>
       <c r="O66" t="n">
         <v>0.39</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>14.4</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H67" t="n">
-        <v>602.7</v>
+        <v>630.6</v>
       </c>
       <c r="I67" t="n">
         <v>605.8561836522701</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>-13.8</v>
+        <v>-19.07</v>
       </c>
       <c r="L67" t="n">
-        <v>15.56</v>
+        <v>21.68</v>
       </c>
       <c r="M67" t="n">
         <v>0.6899999999999999</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>11.58</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H68" t="n">
-        <v>575.45</v>
+        <v>551.4</v>
       </c>
       <c r="I68" t="n">
         <v>565.2295368055181</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K68" t="n">
-        <v>-8.75</v>
+        <v>-12.56</v>
       </c>
       <c r="L68" t="n">
-        <v>9.98</v>
+        <v>12.92</v>
       </c>
       <c r="M68" t="n">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="N68" t="n">
-        <v>2.25</v>
+        <v>4.18</v>
       </c>
       <c r="O68" t="n">
         <v>4.63</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>12.84</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H69" t="n">
-        <v>562.1</v>
+        <v>591.35</v>
       </c>
       <c r="I69" t="n">
         <v>583.2412289788183</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.94</v>
+        <v>-7.25</v>
       </c>
       <c r="L69" t="n">
         <v>10.48</v>
@@ -4374,7 +5201,7 @@
         <v>4.49</v>
       </c>
       <c r="N69" t="n">
-        <v>4.15</v>
+        <v>5.2</v>
       </c>
       <c r="O69" t="n">
         <v>-4.18</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>18.25</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H70" t="n">
-        <v>609.25</v>
+        <v>522.35</v>
       </c>
       <c r="I70" t="n">
         <v>563.1369463921823</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K70" t="n">
-        <v>3.03</v>
+        <v>-11.67</v>
       </c>
       <c r="L70" t="n">
-        <v>5.18</v>
+        <v>12.49</v>
       </c>
       <c r="M70" t="n">
         <v>5.23</v>
       </c>
       <c r="N70" t="n">
-        <v>3.94</v>
+        <v>14.26</v>
       </c>
       <c r="O70" t="n">
         <v>5.2</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>24.53</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H71" t="n">
-        <v>486.85</v>
+        <v>537.9</v>
       </c>
       <c r="I71" t="n">
         <v>527.6595230428104</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K71" t="n">
-        <v>6.8</v>
+        <v>-2.98</v>
       </c>
       <c r="L71" t="n">
         <v>14.67</v>
@@ -4488,7 +5339,7 @@
         <v>6.91</v>
       </c>
       <c r="N71" t="n">
-        <v>9.460000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="O71" t="n">
         <v>-14.26</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>21.07</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H72" t="n">
-        <v>510.4</v>
+        <v>493.9</v>
       </c>
       <c r="I72" t="n">
         <v>495.2762107674799</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.11</v>
+        <v>-8.18</v>
       </c>
       <c r="L72" t="n">
-        <v>8.02</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M72" t="n">
         <v>1.04</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>14.33</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="H73" t="n">
-        <v>492.8</v>
+        <v>527.45</v>
       </c>
       <c r="I73" t="n">
         <v>518.0824227883198</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K73" t="n">
-        <v>0.22</v>
+        <v>-6.79</v>
       </c>
       <c r="L73" t="n">
-        <v>3.98</v>
+        <v>7.66</v>
       </c>
       <c r="M73" t="n">
         <v>2.7</v>
       </c>
       <c r="N73" t="n">
-        <v>5.29</v>
+        <v>7.03</v>
       </c>
       <c r="O73" t="n">
         <v>-3.23</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>15.3</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="H74" t="n">
-        <v>566</v>
+        <v>553.9</v>
       </c>
       <c r="I74" t="n">
         <v>559.0517617010812</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K74" t="n">
-        <v>7.31</v>
+        <v>5.01</v>
       </c>
       <c r="L74" t="n">
         <v>6.82</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4695,25 +5594,25 @@
         <v>10.26</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="H75" t="n">
-        <v>500.55</v>
+        <v>536.1</v>
       </c>
       <c r="I75" t="n">
         <v>519.0121041145637</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K75" t="n">
-        <v>9.630000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="L75" t="n">
         <v>3.29</v>
       </c>
       <c r="M75" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="N75" t="n">
         <v>8.19</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4776,6 +5687,12 @@
       <c r="Q76" t="n">
         <v>1</v>
       </c>
+      <c r="R76" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9734,7 +10651,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="6">
@@ -9744,7 +10661,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -9754,7 +10671,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8">
@@ -9764,7 +10681,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9774,7 +10691,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63.8</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="10">
@@ -9784,7 +10701,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>129.4</v>
       </c>
     </row>
     <row r="11">
@@ -9794,7 +10711,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -9804,7 +10721,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9814,7 +10731,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="14">
@@ -9824,7 +10741,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.12</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="15">
@@ -9834,7 +10751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="16">
@@ -9844,7 +10761,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.24</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="17">
@@ -9854,7 +10771,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>240.22</v>
+        <v>200.5</v>
       </c>
     </row>
     <row r="18">
@@ -9864,7 +10781,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.7</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="19">
@@ -9874,7 +10791,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.99</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="20">
@@ -9884,7 +10801,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10.26</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="21">
@@ -9894,7 +10811,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.8</v>
+        <v>29.49</v>
       </c>
     </row>
     <row r="22">
@@ -9904,7 +10821,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -9914,7 +10831,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -9924,7 +10841,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.98</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="25">
@@ -9934,7 +10851,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.06</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="26">
@@ -9944,7 +10861,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8.16</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="27">
@@ -9964,7 +10881,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
